--- a/Medical/web/public/resources/locum/doctor-take-home-model.xlsx
+++ b/Medical/web/public/resources/locum/doctor-take-home-model.xlsx
@@ -28,6 +28,7 @@
     <definedName name="In_Expenses">'Your figures'!$B$4</definedName>
     <definedName name="In_Pension">'Your figures'!$B$5</definedName>
     <definedName name="In_StudentLoanPlan">'Your figures'!$B$6</definedName>
+    <definedName name="Profit">'Your figures'!$B$7</definedName>
     <definedName name="NetIncome">'Your figures'!$B$8</definedName>
     <definedName name="TaxableIncome">'Your figures'!$B$9</definedName>
     <definedName name="IncomeTax">'Your figures'!$B$10</definedName>
@@ -41,42 +42,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
-  <si>
-    <t>Locked rates: do not edit (2025/26 basis)</t>
-  </si>
-  <si>
-    <t>Income tax: personal allowance (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Income tax: basic rate upper limit (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Income tax: higher rate upper limit (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Class 4 NIC: lower profits limit (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Class 4 NIC: upper profits limit (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Class 4 NIC: main rate (6%, between lower and upper limit): 2025/26</t>
-  </si>
-  <si>
-    <t>Class 4 NIC: upper rate (2%, above upper limit): 2025/26</t>
-  </si>
-  <si>
-    <t>Student loan Plan 1: repayment threshold (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Student loan Plan 2: repayment threshold (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Student loan Plan 4: repayment threshold (GBP): 2025/26</t>
-  </si>
-  <si>
-    <t>Student loan repayment rate (9% of income above threshold): 2025/26</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="78">
+  <si>
+    <t>Locked rates: do not edit (2026/27 basis, verified 26 August 2026)</t>
+  </si>
+  <si>
+    <t>Income tax: personal allowance (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Income tax: basic rate upper limit (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Income tax: higher rate upper limit (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Class 4 NIC: lower profits limit (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Class 4 NIC: upper profits limit (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Class 4 NIC: main rate (6%, between lower and upper limit): 2026/27</t>
+  </si>
+  <si>
+    <t>Class 4 NIC: upper rate (2%, above upper limit): 2026/27</t>
+  </si>
+  <si>
+    <t>Student loan Plan 1: repayment threshold (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Student loan Plan 2: repayment threshold (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Student loan Plan 4: repayment threshold (GBP): 2026/27</t>
+  </si>
+  <si>
+    <t>Student loan repayment rate (9% of income above threshold): 2026/27</t>
   </si>
   <si>
     <t>Your figures: edit the highlighted cells</t>
@@ -100,10 +101,16 @@
     <t>Personal pension contributions (GBP)</t>
   </si>
   <si>
+    <t>Trading profit (Class 4 base)</t>
+  </si>
+  <si>
+    <t>Student loan plan (0=none, 1=Plan1, 2=Plan2, 4=Plan4)</t>
+  </si>
+  <si>
     <t>Pension contributions</t>
   </si>
   <si>
-    <t>Student loan plan (0=none, 1=Plan1, 2=Plan2, 4=Plan4)</t>
+    <t>Trading profit after expenses (GBP): the Class 4 NIC base</t>
   </si>
   <si>
     <t>Net income</t>
@@ -118,7 +125,7 @@
     <t>Taxable income after personal allowance (GBP)</t>
   </si>
   <si>
-    <t>Class 4 NIC</t>
+    <t>Class 4 NIC (on profit)</t>
   </si>
   <si>
     <t>Income tax (GBP)</t>
@@ -127,7 +134,7 @@
     <t>Student loan</t>
   </si>
   <si>
-    <t>Class 4 National Insurance (GBP)</t>
+    <t>Class 4 National Insurance (GBP): charged on profit, before pension</t>
   </si>
   <si>
     <t>Total deductions</t>
@@ -163,7 +170,7 @@
     <t>This model shows your estimated take-home pay as a locum or self-employed</t>
   </si>
   <si>
-    <t>doctor, after income tax, Class 4 NIC and student loan, based on 2025/26 rates.</t>
+    <t>doctor, after income tax, Class 4 NIC and student loan, based on 2026/27 rates.</t>
   </si>
   <si>
     <t>How to use:</t>
@@ -187,7 +194,16 @@
     <t>a required payment from 6 April 2024.</t>
   </si>
   <si>
-    <t>The 'Rates' tab holds the locked 2025/26 rates. Do not edit it.</t>
+    <t>Class 4 is charged on your TRADING PROFIT, which is gross fees less expenses.</t>
+  </si>
+  <si>
+    <t>Your pension contribution does not reduce it. Row 7 shows the profit the Class 4</t>
+  </si>
+  <si>
+    <t>line is built on, and it is deliberately higher than the net income figure below it.</t>
+  </si>
+  <si>
+    <t>The 'Rates' tab holds the locked 2026/27 rates. Do not edit it.</t>
   </si>
   <si>
     <t>See 'Notes' for assumptions and limitations.</t>
@@ -196,10 +212,10 @@
     <t>Assumptions and limitations</t>
   </si>
   <si>
-    <t>2025/26 rates: personal allowance GBP12,570; basic rate 20% to GBP50,270;</t>
-  </si>
-  <si>
-    <t>higher rate 40% to GBP125,140; additional rate 45% above.</t>
+    <t>2026/27 rates, verified at gov.uk on 26 August 2026: personal allowance GBP12,570;</t>
+  </si>
+  <si>
+    <t>basic rate 20% to GBP50,270; higher rate 40% to GBP125,140; additional rate 45% above.</t>
   </si>
   <si>
     <t>Class 4 NIC: 6% on profits between GBP12,570 and GBP50,270, 2% above.</t>
@@ -208,6 +224,30 @@
     <t>Class 2 NIC: removed as a required payment from 6 April 2024 and is NOT included.</t>
   </si>
   <si>
+    <t>Class 4 is charged on trading profit (gross fees less expenses). A personal pension</t>
+  </si>
+  <si>
+    <t>contribution does NOT reduce that profit: relief is given against income tax by</t>
+  </si>
+  <si>
+    <t>extending your basic rate band, not as a business deduction. This model therefore</t>
+  </si>
+  <si>
+    <t>computes Class 4 on row 7 (profit), not on row 8 (net income after pension).</t>
+  </si>
+  <si>
+    <t>Income tax in this model is calculated on net income after the pension contribution.</t>
+  </si>
+  <si>
+    <t>That is a simplification of band extension. It lands in the same place for a</t>
+  </si>
+  <si>
+    <t>straightforward higher-rate case and diverges where the GBP100,000 personal</t>
+  </si>
+  <si>
+    <t>allowance taper or the additional rate is in play.</t>
+  </si>
+  <si>
     <t>This model covers self-employed and locum income (sole trader or PSC/outside-IR35).</t>
   </si>
   <si>
@@ -220,10 +260,10 @@
     <t>and basic-rate band first.</t>
   </si>
   <si>
-    <t>Student loan thresholds (2025/26): Plan 1 GBP26,065; Plan 2 GBP28,470; Plan 4 GBP32,745.</t>
-  </si>
-  <si>
-    <t>All repaid at 9% on income above the threshold.</t>
+    <t>Student loan thresholds (2026/27): Plan 1 GBP26,900; Plan 2 GBP29,385; Plan 4 GBP33,795.</t>
+  </si>
+  <si>
+    <t>All repaid at 9% on income above the threshold. Plan 5 is not modelled.</t>
   </si>
   <si>
     <t>MTD for ITSA: if gross self-employed income is over GBP50,000 you are in Making Tax</t>
@@ -339,11 +379,11 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -764,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>26065</v>
+        <v>26900</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -772,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="4">
-        <v>28470</v>
+        <v>29385</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -780,7 +820,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="4">
-        <v>32745</v>
+        <v>33795</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -861,36 +901,50 @@
       <c r="B5" s="9">
         <v>10000</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="10">
-        <f>In_Pension</f>
+      <c r="E5" s="12">
+        <f>Profit</f>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="13">
         <v>0</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="10">
+        <f>In_Pension</f>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="10">
+        <f>MAX(0,In_GrossIncome-In_Expenses)</f>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="12">
         <f>NetIncome</f>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" s="10">
         <f>MAX(0,In_GrossIncome-In_Expenses-In_Pension)</f>
       </c>
       <c r="D8" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8" s="10">
         <f>IncomeTax</f>
@@ -898,13 +952,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="10">
         <f>MAX(0,NetIncome-PA)</f>
       </c>
       <c r="D9" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E9" s="10">
         <f>Class4</f>
@@ -912,13 +966,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10">
         <f>LET(t,TaxableIncome,basic,MIN(t,BRL-PA),higher,IF(t&gt;BRL-PA,MIN(t-(BRL-PA),HRL-BRL),0),additional,IF(t&gt;HRL-PA,t-(HRL-PA),0),basic*0.2+higher*0.4+additional*0.45)</f>
       </c>
       <c r="D10" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E10" s="10">
         <f>StudentLoan</f>
@@ -926,21 +980,21 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B11" s="10">
-        <f>IF(NetIncome&lt;=NI_LOWER,0,(MIN(NetIncome,NI_UPPER)-NI_LOWER)*C4_MAIN+MAX(0,NetIncome-NI_UPPER)*C4_UPPER_RATE)</f>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="13">
+        <f>IF(Profit&lt;=NI_LOWER,0,(MIN(Profit,NI_UPPER)-NI_LOWER)*C4_MAIN+MAX(0,Profit-NI_UPPER)*C4_UPPER_RATE)</f>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="12">
         <f>TotalDeductions</f>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" s="10">
         <f>IF(In_StudentLoanPlan=0,0,IF(In_StudentLoanPlan=1,MAX(0,NetIncome-SL_PLAN1)*SL_RATE,IF(In_StudentLoanPlan=2,MAX(0,NetIncome-SL_PLAN2)*SL_RATE,IF(In_StudentLoanPlan=4,MAX(0,NetIncome-SL_PLAN4)*SL_RATE,0))))</f>
@@ -948,29 +1002,29 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B13" s="15">
         <f>IncomeTax+Class4+StudentLoan</f>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="13">
+      <c r="D13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="12">
         <f>NetTakeHome</f>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="13">
+        <v>35</v>
+      </c>
+      <c r="B14" s="12">
         <f>NetIncome-TotalDeductions</f>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5">
         <f>IF(NetIncome&gt;0,TotalDeductions/NetIncome,0)</f>
@@ -978,7 +1032,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <f>IF(ABS(NetTakeHome+TotalDeductions-NetIncome)&lt;0.01,"OK","ERROR")</f>
@@ -999,7 +1053,7 @@
   <sheetPr>
     <tabColor rgb="FFb87333"/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
@@ -1007,92 +1061,112 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>48</v>
+      <c r="A17" s="17" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1103,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
@@ -1111,107 +1185,157 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
